--- a/results/Int Task Remove ACC -1.0/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_9_permute.xlsx
@@ -440,877 +440,877 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6266894454550946</v>
+        <v>0.6267780544945593</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6229754177043546</v>
+        <v>0.6282365794225644</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6217917821828702</v>
+        <v>0.6282365794225644</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.626190851787956</v>
+        <v>0.6371233276722003</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6367084762601615</v>
+        <v>0.6168801898381542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6452409561720895</v>
+        <v>0.6072572145882701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6473611959535206</v>
+        <v>0.6043866509139486</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6362749968114172</v>
+        <v>0.616763890473857</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6304873832810853</v>
+        <v>0.6140564479858226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6505627009646302</v>
+        <v>0.6156827930643288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6515973121924696</v>
+        <v>0.6086368640455397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6522449301532534</v>
+        <v>0.6239076586403882</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.652044552893555</v>
+        <v>0.6241686189744176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6536475709711416</v>
+        <v>0.6254920486812693</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6674831676389048</v>
+        <v>0.6163351099893266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6676649168618974</v>
+        <v>0.6187862911075459</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6694221616577946</v>
+        <v>0.624089407863381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6697670320670743</v>
+        <v>0.6237678644550209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6800379609180434</v>
+        <v>0.6279106726902912</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.680056588954749</v>
+        <v>0.6312845289959657</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6812774805496445</v>
+        <v>0.6832112721438688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6854108908564869</v>
+        <v>0.7045915593177103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6838451288523115</v>
+        <v>0.7045915593177103</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6838451288523115</v>
+        <v>0.7045915593177103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6933331767011929</v>
+        <v>0.7173366606475173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6933937597755238</v>
+        <v>0.739891185414415</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6778014217723151</v>
+        <v>0.741317153233223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6850759218360867</v>
+        <v>0.7415036014204297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6816228544193759</v>
+        <v>0.7413265511616511</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.681944397827736</v>
+        <v>0.7510146406299296</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6832678275345877</v>
+        <v>0.7490340272137156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6853182541334103</v>
+        <v>0.7507209553665528</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6839295423880136</v>
+        <v>0.7530882264095214</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6739291396196524</v>
+        <v>0.744415952312226</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7003329551785942</v>
+        <v>0.7440524538662405</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6826062805013123</v>
+        <v>0.7394718028583128</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.698785653390974</v>
+        <v>0.7621427948096584</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6838082084192013</v>
+        <v>0.7581307184716283</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6762915438782566</v>
+        <v>0.7581307184716283</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6862219656438588</v>
+        <v>0.7480185474830334</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6704524095617208</v>
+        <v>0.7487222173740845</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6634204096154233</v>
+        <v>0.7792871335647014</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6637792090971948</v>
+        <v>0.7792638065637817</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6472361699413972</v>
+        <v>0.7729633346535185</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6472361699413972</v>
+        <v>0.7285299290456404</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6614914848055635</v>
+        <v>0.7287303063053387</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6594224301700353</v>
+        <v>0.737607824446697</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6610301472118361</v>
+        <v>0.7393927595674268</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6643620484798851</v>
+        <v>0.7331063845498056</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6260426665950634</v>
+        <v>0.7291921473595178</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6265645872631218</v>
+        <v>0.7167170686518671</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6350690412099161</v>
+        <v>0.7197087984748505</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6350690412099161</v>
+        <v>0.7172341225355612</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6297892514550008</v>
+        <v>0.735865347824044</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6074629620927845</v>
+        <v>0.7387125844974458</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5916373540803792</v>
+        <v>0.7321699481100095</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6133668749874135</v>
+        <v>0.7362147493773872</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6042379622606046</v>
+        <v>0.737090770563003</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6306231497828407</v>
+        <v>0.7318438735575858</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.631648363082252</v>
+        <v>0.7465788184118843</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6222539588773504</v>
+        <v>0.7262888587558485</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5851605031919392</v>
+        <v>0.7262888587558485</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5576202095738039</v>
+        <v>0.7393185830609053</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5467063617262652</v>
+        <v>0.7718545469191577</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5467063617262652</v>
+        <v>0.7712300881391431</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5491155878068591</v>
+        <v>0.7675021313159114</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4782651088481497</v>
+        <v>0.7156354677818875</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4876830078741214</v>
+        <v>0.7156354677818875</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.511411938054226</v>
+        <v>0.7263767965147111</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5120922809443575</v>
+        <v>0.7077509414710443</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5185976612583826</v>
+        <v>0.693798709798683</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5215610294759312</v>
+        <v>0.6938317703683317</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5227211701763455</v>
+        <v>0.6825869811840046</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5408907222307997</v>
+        <v>0.6895119118742825</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5292965314931295</v>
+        <v>0.6765801945371184</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5162948331532063</v>
+        <v>0.6801544281024912</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5632215427370795</v>
+        <v>0.6752101108284274</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5249261591337795</v>
+        <v>0.6650791439829764</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5072741644234706</v>
+        <v>0.6540488289509898</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5030615430055918</v>
+        <v>0.627095738039458</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5026607884861951</v>
+        <v>0.6266288623807638</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5032060361551732</v>
+        <v>0.6085762809712087</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5074419845739717</v>
+        <v>0.6137582315783821</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5042126214178788</v>
+        <v>0.5952392779705844</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5022461048943069</v>
+        <v>0.5922755741127348</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5019851445602777</v>
+        <v>0.5920377729594748</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5010997254462338</v>
+        <v>0.5669803784680034</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5007781820378736</v>
+        <v>0.5663651497962664</v>
       </c>
     </row>
     <row r="90">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.499617873517309</v>
+        <v>0.4991132383247521</v>
       </c>
     </row>
   </sheetData>
